--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0F5224-3B75-494E-A0DA-63986F3B745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922CAA3C-0DE0-4706-9612-14505A702817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="915">
   <si>
     <t>Recensore</t>
   </si>
@@ -2666,9 +2666,6 @@
   </si>
   <si>
     <t>Fernanda D'Arienzo</t>
-  </si>
-  <si>
-    <t>bloccato per Andrea Magnani</t>
   </si>
   <si>
     <t>bloccato per Francesca Vasciaveo</t>
@@ -3722,15 +3719,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3752,15 +3749,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>615</v>
@@ -3853,7 +3850,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3861,7 +3858,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3922,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="25">
@@ -4036,7 +4033,7 @@
         <v>718</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4290,7 +4287,7 @@
         <v>700</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4392,7 +4389,7 @@
         <v>236</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>107</v>
@@ -4416,7 +4413,7 @@
         <v>680</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O11" s="35">
         <v>1</v>
@@ -4792,7 +4789,7 @@
         <v>195</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4886,20 +4883,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>278</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>190</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
@@ -5154,7 +5151,7 @@
         <v>699</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5278,7 +5275,7 @@
         <v>812</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5902,7 +5899,7 @@
         <v>246</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O23" s="35">
         <v>1</v>
@@ -6028,7 +6025,7 @@
         <v>510</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O24" s="35">
         <v>1</v>
@@ -6154,7 +6151,7 @@
         <v>195</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O25" s="35">
         <v>1</v>
@@ -6280,7 +6277,7 @@
         <v>195</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O26" s="35">
         <v>1</v>
@@ -6656,7 +6653,7 @@
         <v>701</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6780,7 +6777,7 @@
         <v>793</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O30" s="35">
         <v>1</v>
@@ -6906,14 +6903,14 @@
         <v>702</v>
       </c>
       <c r="N31" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O31" s="35">
         <v>1</v>
       </c>
       <c r="P31" s="33"/>
       <c r="Q31" s="34" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="2">
@@ -7034,7 +7031,7 @@
         <v>246</v>
       </c>
       <c r="N32" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O32" s="35">
         <v>1</v>
@@ -7492,22 +7489,22 @@
         <v>3</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E36" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="J36" s="33"/>
       <c r="K36" s="33" t="s">
@@ -7517,17 +7514,17 @@
         <v>55</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N36" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O36" s="35">
         <v>1</v>
       </c>
       <c r="P36" s="33"/>
       <c r="Q36" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="2">
@@ -7608,51 +7605,53 @@
       <c r="AT36" s="13"/>
     </row>
     <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="36">
-        <v>0</v>
-      </c>
-      <c r="B37" s="36">
-        <v>1</v>
-      </c>
-      <c r="C37" s="36">
+      <c r="A37" s="33">
+        <v>0</v>
+      </c>
+      <c r="B37" s="33">
+        <v>1</v>
+      </c>
+      <c r="C37" s="33">
         <v>3</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="34" t="s">
         <v>524</v>
       </c>
-      <c r="E37" s="37" t="s">
+      <c r="E37" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="34" t="s">
         <v>525</v>
       </c>
-      <c r="G37" s="37" t="s">
+      <c r="G37" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="H37" s="37" t="s">
+      <c r="H37" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I37" s="36" t="s">
+      <c r="I37" s="33" t="s">
         <v>560</v>
       </c>
-      <c r="J37" s="36">
+      <c r="J37" s="33">
         <v>7</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="K37" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L37" s="36" t="s">
+      <c r="L37" s="33" t="s">
         <v>505</v>
       </c>
-      <c r="M37" s="37" t="s">
+      <c r="M37" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="N37" s="37" t="s">
-        <v>849</v>
-      </c>
-      <c r="O37" s="38"/>
-      <c r="P37" s="36"/>
-      <c r="Q37" s="37"/>
+      <c r="N37" s="34" t="s">
+        <v>856</v>
+      </c>
+      <c r="O37" s="35">
+        <v>1</v>
+      </c>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="34"/>
       <c r="R37" s="13"/>
       <c r="S37" s="2">
         <f t="shared" si="23"/>
@@ -7701,7 +7700,7 @@
       </c>
       <c r="AE37" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" s="2">
         <f t="shared" si="19"/>
@@ -7709,7 +7708,7 @@
       </c>
       <c r="AG37" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" s="2">
         <f t="shared" si="21"/>
@@ -7860,51 +7859,53 @@
       <c r="AT38" s="13"/>
     </row>
     <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36">
-        <v>0</v>
-      </c>
-      <c r="B39" s="36">
-        <v>1</v>
-      </c>
-      <c r="C39" s="36">
+      <c r="A39" s="33">
+        <v>0</v>
+      </c>
+      <c r="B39" s="33">
+        <v>1</v>
+      </c>
+      <c r="C39" s="33">
         <v>3</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="E39" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="34" t="s">
         <v>586</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="34" t="s">
         <v>660</v>
       </c>
-      <c r="I39" s="36" t="s">
+      <c r="I39" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="J39" s="36">
+      <c r="J39" s="33">
         <v>99</v>
       </c>
-      <c r="K39" s="36" t="s">
+      <c r="K39" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="L39" s="36">
+      <c r="L39" s="33">
         <v>65</v>
       </c>
-      <c r="M39" s="37" t="s">
+      <c r="M39" s="34" t="s">
         <v>794</v>
       </c>
-      <c r="N39" s="37" t="s">
-        <v>851</v>
-      </c>
-      <c r="O39" s="38"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="37"/>
+      <c r="N39" s="34" t="s">
+        <v>855</v>
+      </c>
+      <c r="O39" s="35">
+        <v>1</v>
+      </c>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="34"/>
       <c r="R39" s="13"/>
       <c r="S39" s="2">
         <f t="shared" si="23"/>
@@ -7953,7 +7954,7 @@
       </c>
       <c r="AE39" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" s="2">
         <f t="shared" si="19"/>
@@ -7961,7 +7962,7 @@
       </c>
       <c r="AG39" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="2">
         <f t="shared" si="21"/>
@@ -8146,7 +8147,7 @@
         <v>795</v>
       </c>
       <c r="N41" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="36"/>
@@ -8270,7 +8271,7 @@
         <v>694</v>
       </c>
       <c r="N42" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O42" s="35">
         <v>1</v>
@@ -9006,7 +9007,7 @@
         <v>513</v>
       </c>
       <c r="N48" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O48" s="35">
         <v>1</v>
@@ -9132,7 +9133,7 @@
         <v>678</v>
       </c>
       <c r="N49" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O49" s="35">
         <v>1</v>
@@ -9258,7 +9259,7 @@
         <v>302</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9384,7 +9385,7 @@
         <v>195</v>
       </c>
       <c r="N51" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O51" s="35">
         <v>1</v>
@@ -9510,7 +9511,7 @@
         <v>674</v>
       </c>
       <c r="N52" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O52" s="35">
         <v>1</v>
@@ -9758,7 +9759,7 @@
         <v>302</v>
       </c>
       <c r="N54" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O54" s="35">
         <v>1</v>
@@ -9860,7 +9861,7 @@
         <v>235</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G55" s="34" t="s">
         <v>490</v>
@@ -9884,7 +9885,7 @@
         <v>265</v>
       </c>
       <c r="N55" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O55" s="35">
         <v>1</v>
@@ -10013,7 +10014,7 @@
       <c r="O56" s="41"/>
       <c r="P56" s="39"/>
       <c r="Q56" s="40" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R56" s="13"/>
       <c r="S56" s="2">
@@ -10104,13 +10105,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E57" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F57" s="34" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G57" s="34" t="s">
         <v>109</v>
@@ -10119,7 +10120,7 @@
         <v>190</v>
       </c>
       <c r="I57" s="33" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J57" s="33"/>
       <c r="K57" s="33" t="s">
@@ -10634,7 +10635,7 @@
         <v>675</v>
       </c>
       <c r="N61" s="37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O61" s="38"/>
       <c r="P61" s="36"/>
@@ -11370,7 +11371,7 @@
         <v>677</v>
       </c>
       <c r="N67" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O67" s="35">
         <v>1</v>
@@ -11496,7 +11497,7 @@
         <v>703</v>
       </c>
       <c r="N68" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O68" s="35">
         <v>1</v>
@@ -11622,7 +11623,7 @@
         <v>195</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O69" s="35">
         <v>1</v>
@@ -11718,13 +11719,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>840</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>72</v>
@@ -11733,7 +11734,7 @@
         <v>190</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="J70" s="20">
         <v>4</v>
@@ -11745,7 +11746,7 @@
         <v>45</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N70" s="19"/>
       <c r="O70" s="18"/>
@@ -11868,7 +11869,7 @@
         <v>817</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O71" s="35">
         <v>1</v>
@@ -11994,7 +11995,7 @@
         <v>712</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -12120,7 +12121,7 @@
         <v>513</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O73" s="35">
         <v>1</v>
@@ -12246,7 +12247,7 @@
         <v>513</v>
       </c>
       <c r="N74" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O74" s="35">
         <v>1</v>
@@ -12613,10 +12614,10 @@
         <v>70</v>
       </c>
       <c r="M77" s="34" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N77" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O77" s="35">
         <v>1</v>
@@ -12989,7 +12990,7 @@
       <c r="O80" s="18"/>
       <c r="P80" s="20"/>
       <c r="Q80" s="19" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R80" s="13"/>
       <c r="S80" s="2">
@@ -13110,7 +13111,7 @@
         <v>508</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13364,7 +13365,7 @@
         <v>248</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13618,7 +13619,7 @@
         <v>711</v>
       </c>
       <c r="N85" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O85" s="35">
         <v>1</v>
@@ -13714,13 +13715,13 @@
         <v>6</v>
       </c>
       <c r="D86" s="34" t="s">
+        <v>879</v>
+      </c>
+      <c r="E86" s="34" t="s">
         <v>880</v>
       </c>
-      <c r="E86" s="34" t="s">
+      <c r="F86" s="34" t="s">
         <v>881</v>
-      </c>
-      <c r="F86" s="34" t="s">
-        <v>882</v>
       </c>
       <c r="G86" s="34" t="s">
         <v>88</v>
@@ -13729,7 +13730,7 @@
         <v>190</v>
       </c>
       <c r="I86" s="33" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J86" s="33">
         <v>2</v>
@@ -13741,10 +13742,10 @@
         <v>45</v>
       </c>
       <c r="M86" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="N86" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O86" s="35">
         <v>1</v>
@@ -13867,7 +13868,7 @@
         <v>516</v>
       </c>
       <c r="N87" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O87" s="35">
         <v>1</v>
@@ -13990,7 +13991,7 @@
         <v>516</v>
       </c>
       <c r="N88" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -14116,7 +14117,7 @@
         <v>248</v>
       </c>
       <c r="N89" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O89" s="35">
         <v>1</v>
@@ -14212,20 +14213,20 @@
         <v>6</v>
       </c>
       <c r="D90" s="34" t="s">
+        <v>861</v>
+      </c>
+      <c r="E90" s="34" t="s">
         <v>862</v>
       </c>
-      <c r="E90" s="34" t="s">
+      <c r="F90" s="34" t="s">
         <v>863</v>
-      </c>
-      <c r="F90" s="34" t="s">
-        <v>864</v>
       </c>
       <c r="G90" s="34"/>
       <c r="H90" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I90" s="33" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J90" s="33"/>
       <c r="K90" s="33" t="s">
@@ -14362,7 +14363,7 @@
         <v>195</v>
       </c>
       <c r="N91" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O91" s="35">
         <v>1</v>
@@ -14488,7 +14489,7 @@
         <v>704</v>
       </c>
       <c r="N92" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O92" s="35">
         <v>1</v>
@@ -14736,7 +14737,7 @@
         <v>627</v>
       </c>
       <c r="N94" s="40" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O94" s="41">
         <v>1</v>
@@ -15127,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="34" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="R97" s="13"/>
       <c r="S97" s="2">
@@ -15248,7 +15249,7 @@
         <v>268</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15374,7 +15375,7 @@
         <v>268</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15500,7 +15501,7 @@
         <v>833</v>
       </c>
       <c r="N100" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O100" s="35">
         <v>1</v>
@@ -15626,7 +15627,7 @@
         <v>195</v>
       </c>
       <c r="N101" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O101" s="35">
         <v>1</v>
@@ -15874,7 +15875,7 @@
         <v>804</v>
       </c>
       <c r="N103" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O103" s="35">
         <v>1</v>
@@ -16000,7 +16001,7 @@
         <v>563</v>
       </c>
       <c r="N104" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O104" s="35">
         <v>1</v>
@@ -16126,7 +16127,7 @@
         <v>249</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16350,13 +16351,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E107" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>88</v>
@@ -16365,7 +16366,7 @@
         <v>190</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J107" s="33">
         <v>2</v>
@@ -16377,7 +16378,7 @@
         <v>5</v>
       </c>
       <c r="M107" s="34" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="N107" s="34" t="s">
         <v>848</v>
@@ -16389,7 +16390,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="34" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R107" s="13"/>
       <c r="S107" s="2">
@@ -16519,7 +16520,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="34" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R108" s="13"/>
       <c r="S108" s="2">
@@ -16610,7 +16611,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E109" s="34" t="s">
         <v>756</v>
@@ -17262,7 +17263,7 @@
         <v>193</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O114" s="35">
         <v>1</v>
@@ -18144,7 +18145,7 @@
         <v>706</v>
       </c>
       <c r="N121" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O121" s="35">
         <v>1</v>
@@ -18265,10 +18266,10 @@
         <v>30</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18522,7 +18523,7 @@
         <v>726</v>
       </c>
       <c r="N124" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O124" s="35">
         <v>1</v>
@@ -18990,7 +18991,7 @@
         <v>382</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>204</v>
@@ -19472,18 +19473,18 @@
         <v>2</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E132" s="34"/>
       <c r="F132" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G132" s="34"/>
       <c r="H132" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I132" s="33" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J132" s="33"/>
       <c r="K132" s="33" t="s">
@@ -19493,7 +19494,7 @@
         <v>22</v>
       </c>
       <c r="M132" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="N132" s="34" t="s">
         <v>848</v>
@@ -19752,7 +19753,7 @@
         <v>456</v>
       </c>
       <c r="N134" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O134" s="35">
         <v>1</v>
@@ -20000,7 +20001,7 @@
         <v>667</v>
       </c>
       <c r="N136" s="37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O136" s="38"/>
       <c r="P136" s="36"/>
@@ -20606,13 +20607,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="34" t="s">
+        <v>872</v>
+      </c>
+      <c r="E141" s="34" t="s">
+        <v>871</v>
+      </c>
+      <c r="F141" s="34" t="s">
         <v>873</v>
-      </c>
-      <c r="E141" s="34" t="s">
-        <v>872</v>
-      </c>
-      <c r="F141" s="34" t="s">
-        <v>874</v>
       </c>
       <c r="G141" s="34" t="s">
         <v>137</v>
@@ -20736,7 +20737,7 @@
         <v>635</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G142" s="34" t="s">
         <v>83</v>
@@ -20769,7 +20770,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="34" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="R142" s="13"/>
       <c r="S142" s="2">
@@ -21264,7 +21265,7 @@
         <v>668</v>
       </c>
       <c r="N146" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O146" s="38"/>
       <c r="P146" s="36"/>
@@ -21510,7 +21511,7 @@
         <v>622</v>
       </c>
       <c r="N148" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O148" s="35">
         <v>1</v>
@@ -21636,7 +21637,7 @@
         <v>514</v>
       </c>
       <c r="N149" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O149" s="35">
         <v>1</v>
@@ -22137,7 +22138,7 @@
         <v>669</v>
       </c>
       <c r="N153" s="40" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O153" s="41"/>
       <c r="P153" s="39"/>
@@ -22499,7 +22500,7 @@
         <v>817</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22625,7 +22626,7 @@
         <v>729</v>
       </c>
       <c r="N157" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O157" s="35">
         <v>1</v>
@@ -22873,7 +22874,7 @@
         <v>843</v>
       </c>
       <c r="N159" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="O159" s="35">
         <v>1</v>
@@ -22995,7 +22996,7 @@
         <v>828</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -23121,7 +23122,7 @@
         <v>461</v>
       </c>
       <c r="N161" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O161" s="35">
         <v>1</v>
@@ -23610,7 +23611,7 @@
         <v>744</v>
       </c>
       <c r="N165" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O165" s="35">
         <v>1</v>
@@ -23962,7 +23963,7 @@
         <v>87</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>100</v>
@@ -24212,7 +24213,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G170" s="34" t="s">
         <v>82</v>
@@ -24468,7 +24469,7 @@
         <v>38</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G172" s="34" t="s">
         <v>758</v>
@@ -24748,7 +24749,7 @@
         <v>196</v>
       </c>
       <c r="N174" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O174" s="35">
         <v>1</v>
@@ -24874,7 +24875,7 @@
         <v>196</v>
       </c>
       <c r="N175" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O175" s="35">
         <v>1</v>
@@ -25869,7 +25870,7 @@
         <v>196</v>
       </c>
       <c r="N183" s="37" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O183" s="38"/>
       <c r="P183" s="36"/>
@@ -27469,7 +27470,7 @@
         <v>55</v>
       </c>
       <c r="F196" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G196" s="34" t="s">
         <v>72</v>
@@ -27478,7 +27479,7 @@
         <v>190</v>
       </c>
       <c r="I196" s="33" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J196" s="33">
         <v>4</v>
@@ -28243,7 +28244,7 @@
         <v>196</v>
       </c>
       <c r="N202" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O202" s="35">
         <v>1</v>
@@ -28369,7 +28370,7 @@
         <v>196</v>
       </c>
       <c r="N203" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O203" s="35">
         <v>1</v>
@@ -28751,7 +28752,7 @@
         <v>196</v>
       </c>
       <c r="N206" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O206" s="35">
         <v>1</v>
@@ -28877,7 +28878,7 @@
         <v>196</v>
       </c>
       <c r="N207" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O207" s="35">
         <v>1</v>
@@ -29860,7 +29861,7 @@
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G215" s="34" t="s">
         <v>145</v>
@@ -30009,7 +30010,7 @@
         <v>312</v>
       </c>
       <c r="N216" s="37" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O216" s="38"/>
       <c r="P216" s="36"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922CAA3C-0DE0-4706-9612-14505A702817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C8E442-BB62-4090-B5F0-A6D4C315DA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3719,15 +3719,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3749,15 +3749,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>615</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -5237,49 +5237,51 @@
       <c r="AT17" s="13"/>
     </row>
     <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36">
-        <v>0</v>
-      </c>
-      <c r="B18" s="36">
-        <v>1</v>
-      </c>
-      <c r="C18" s="36">
+      <c r="A18" s="33">
+        <v>0</v>
+      </c>
+      <c r="B18" s="33">
+        <v>1</v>
+      </c>
+      <c r="C18" s="33">
         <v>2</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="34" t="s">
         <v>811</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="34" t="s">
         <v>813</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="34" t="s">
         <v>656</v>
       </c>
-      <c r="H18" s="37" t="s">
+      <c r="H18" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="33" t="s">
         <v>814</v>
       </c>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36" t="s">
+      <c r="J18" s="33"/>
+      <c r="K18" s="33" t="s">
         <v>385</v>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="33">
         <v>45</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="34" t="s">
         <v>812</v>
       </c>
-      <c r="N18" s="37" t="s">
-        <v>849</v>
-      </c>
-      <c r="O18" s="38"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="37"/>
+      <c r="N18" s="34" t="s">
+        <v>857</v>
+      </c>
+      <c r="O18" s="35">
+        <v>1</v>
+      </c>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="34"/>
       <c r="R18" s="13"/>
       <c r="S18" s="2">
         <f t="shared" si="23"/>
@@ -5328,7 +5330,7 @@
       </c>
       <c r="AE18" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" s="2">
         <f t="shared" si="19"/>
@@ -5336,7 +5338,7 @@
       </c>
       <c r="AG18" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18" s="2">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C8E442-BB62-4090-B5F0-A6D4C315DA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A966C5F-A9AE-4767-9E78-1937257911E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="914">
   <si>
     <t>Recensore</t>
   </si>
@@ -2672,9 +2672,6 @@
   </si>
   <si>
     <t>bloccato per Catia Gribaudo</t>
-  </si>
-  <si>
-    <t>bloccato per Isabella Brandino</t>
   </si>
   <si>
     <t>Trattoria Tarassaco</t>
@@ -3719,15 +3716,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3749,15 +3746,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>615</v>
@@ -3850,7 +3847,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3858,7 +3855,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3919,7 +3916,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="25">
@@ -4033,7 +4030,7 @@
         <v>718</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4287,7 +4284,7 @@
         <v>700</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4389,7 +4386,7 @@
         <v>236</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>107</v>
@@ -4413,7 +4410,7 @@
         <v>680</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O11" s="35">
         <v>1</v>
@@ -4883,20 +4880,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>278</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>190</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
@@ -5151,7 +5148,7 @@
         <v>699</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5275,7 +5272,7 @@
         <v>812</v>
       </c>
       <c r="N18" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O18" s="35">
         <v>1</v>
@@ -5901,7 +5898,7 @@
         <v>246</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O23" s="35">
         <v>1</v>
@@ -6027,7 +6024,7 @@
         <v>510</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O24" s="35">
         <v>1</v>
@@ -6153,7 +6150,7 @@
         <v>195</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O25" s="35">
         <v>1</v>
@@ -6279,7 +6276,7 @@
         <v>195</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O26" s="35">
         <v>1</v>
@@ -6655,7 +6652,7 @@
         <v>701</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6779,7 +6776,7 @@
         <v>793</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O30" s="35">
         <v>1</v>
@@ -6905,14 +6902,14 @@
         <v>702</v>
       </c>
       <c r="N31" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O31" s="35">
         <v>1</v>
       </c>
       <c r="P31" s="33"/>
       <c r="Q31" s="34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="2">
@@ -7033,7 +7030,7 @@
         <v>246</v>
       </c>
       <c r="N32" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O32" s="35">
         <v>1</v>
@@ -7491,22 +7488,22 @@
         <v>3</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E36" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="J36" s="33"/>
       <c r="K36" s="33" t="s">
@@ -7516,17 +7513,17 @@
         <v>55</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N36" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O36" s="35">
         <v>1</v>
       </c>
       <c r="P36" s="33"/>
       <c r="Q36" s="34" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="2">
@@ -7647,7 +7644,7 @@
         <v>195</v>
       </c>
       <c r="N37" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O37" s="35">
         <v>1</v>
@@ -7901,7 +7898,7 @@
         <v>794</v>
       </c>
       <c r="N39" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O39" s="35">
         <v>1</v>
@@ -8273,7 +8270,7 @@
         <v>694</v>
       </c>
       <c r="N42" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O42" s="35">
         <v>1</v>
@@ -9009,7 +9006,7 @@
         <v>513</v>
       </c>
       <c r="N48" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O48" s="35">
         <v>1</v>
@@ -9135,7 +9132,7 @@
         <v>678</v>
       </c>
       <c r="N49" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O49" s="35">
         <v>1</v>
@@ -9261,7 +9258,7 @@
         <v>302</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9387,7 +9384,7 @@
         <v>195</v>
       </c>
       <c r="N51" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O51" s="35">
         <v>1</v>
@@ -9513,7 +9510,7 @@
         <v>674</v>
       </c>
       <c r="N52" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O52" s="35">
         <v>1</v>
@@ -9761,7 +9758,7 @@
         <v>302</v>
       </c>
       <c r="N54" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O54" s="35">
         <v>1</v>
@@ -9863,7 +9860,7 @@
         <v>235</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G55" s="34" t="s">
         <v>490</v>
@@ -9887,7 +9884,7 @@
         <v>265</v>
       </c>
       <c r="N55" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O55" s="35">
         <v>1</v>
@@ -10016,7 +10013,7 @@
       <c r="O56" s="41"/>
       <c r="P56" s="39"/>
       <c r="Q56" s="40" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R56" s="13"/>
       <c r="S56" s="2">
@@ -10107,13 +10104,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E57" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F57" s="34" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G57" s="34" t="s">
         <v>109</v>
@@ -10122,7 +10119,7 @@
         <v>190</v>
       </c>
       <c r="I57" s="33" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J57" s="33"/>
       <c r="K57" s="33" t="s">
@@ -11373,7 +11370,7 @@
         <v>677</v>
       </c>
       <c r="N67" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="O67" s="35">
         <v>1</v>
@@ -11499,7 +11496,7 @@
         <v>703</v>
       </c>
       <c r="N68" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O68" s="35">
         <v>1</v>
@@ -11625,7 +11622,7 @@
         <v>195</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O69" s="35">
         <v>1</v>
@@ -11721,13 +11718,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>840</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>72</v>
@@ -11736,7 +11733,7 @@
         <v>190</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J70" s="20">
         <v>4</v>
@@ -11748,7 +11745,7 @@
         <v>45</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N70" s="19"/>
       <c r="O70" s="18"/>
@@ -11871,7 +11868,7 @@
         <v>817</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O71" s="35">
         <v>1</v>
@@ -11997,7 +11994,7 @@
         <v>712</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -12123,7 +12120,7 @@
         <v>513</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O73" s="35">
         <v>1</v>
@@ -12249,7 +12246,7 @@
         <v>513</v>
       </c>
       <c r="N74" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O74" s="35">
         <v>1</v>
@@ -12616,10 +12613,10 @@
         <v>70</v>
       </c>
       <c r="M77" s="34" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N77" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="O77" s="35">
         <v>1</v>
@@ -12992,7 +12989,7 @@
       <c r="O80" s="18"/>
       <c r="P80" s="20"/>
       <c r="Q80" s="19" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R80" s="13"/>
       <c r="S80" s="2">
@@ -13113,7 +13110,7 @@
         <v>508</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13367,7 +13364,7 @@
         <v>248</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13621,7 +13618,7 @@
         <v>711</v>
       </c>
       <c r="N85" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O85" s="35">
         <v>1</v>
@@ -13717,13 +13714,13 @@
         <v>6</v>
       </c>
       <c r="D86" s="34" t="s">
+        <v>878</v>
+      </c>
+      <c r="E86" s="34" t="s">
         <v>879</v>
       </c>
-      <c r="E86" s="34" t="s">
+      <c r="F86" s="34" t="s">
         <v>880</v>
-      </c>
-      <c r="F86" s="34" t="s">
-        <v>881</v>
       </c>
       <c r="G86" s="34" t="s">
         <v>88</v>
@@ -13732,7 +13729,7 @@
         <v>190</v>
       </c>
       <c r="I86" s="33" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="J86" s="33">
         <v>2</v>
@@ -13744,10 +13741,10 @@
         <v>45</v>
       </c>
       <c r="M86" s="34" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="N86" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O86" s="35">
         <v>1</v>
@@ -13870,7 +13867,7 @@
         <v>516</v>
       </c>
       <c r="N87" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O87" s="35">
         <v>1</v>
@@ -13993,7 +13990,7 @@
         <v>516</v>
       </c>
       <c r="N88" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -14119,7 +14116,7 @@
         <v>248</v>
       </c>
       <c r="N89" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O89" s="35">
         <v>1</v>
@@ -14215,20 +14212,20 @@
         <v>6</v>
       </c>
       <c r="D90" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="E90" s="34" t="s">
         <v>861</v>
       </c>
-      <c r="E90" s="34" t="s">
+      <c r="F90" s="34" t="s">
         <v>862</v>
-      </c>
-      <c r="F90" s="34" t="s">
-        <v>863</v>
       </c>
       <c r="G90" s="34"/>
       <c r="H90" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I90" s="33" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="J90" s="33"/>
       <c r="K90" s="33" t="s">
@@ -14365,7 +14362,7 @@
         <v>195</v>
       </c>
       <c r="N91" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O91" s="35">
         <v>1</v>
@@ -14491,7 +14488,7 @@
         <v>704</v>
       </c>
       <c r="N92" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O92" s="35">
         <v>1</v>
@@ -14739,7 +14736,7 @@
         <v>627</v>
       </c>
       <c r="N94" s="40" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O94" s="41">
         <v>1</v>
@@ -15130,7 +15127,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="34" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R97" s="13"/>
       <c r="S97" s="2">
@@ -15251,7 +15248,7 @@
         <v>268</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15377,7 +15374,7 @@
         <v>268</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15503,7 +15500,7 @@
         <v>833</v>
       </c>
       <c r="N100" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O100" s="35">
         <v>1</v>
@@ -15629,7 +15626,7 @@
         <v>195</v>
       </c>
       <c r="N101" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O101" s="35">
         <v>1</v>
@@ -15877,7 +15874,7 @@
         <v>804</v>
       </c>
       <c r="N103" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O103" s="35">
         <v>1</v>
@@ -16003,7 +16000,7 @@
         <v>563</v>
       </c>
       <c r="N104" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O104" s="35">
         <v>1</v>
@@ -16129,7 +16126,7 @@
         <v>249</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16353,13 +16350,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E107" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>88</v>
@@ -16368,7 +16365,7 @@
         <v>190</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J107" s="33">
         <v>2</v>
@@ -16380,7 +16377,7 @@
         <v>5</v>
       </c>
       <c r="M107" s="34" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="N107" s="34" t="s">
         <v>848</v>
@@ -16392,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="34" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R107" s="13"/>
       <c r="S107" s="2">
@@ -16522,7 +16519,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="34" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R108" s="13"/>
       <c r="S108" s="2">
@@ -16613,7 +16610,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E109" s="34" t="s">
         <v>756</v>
@@ -17265,7 +17262,7 @@
         <v>193</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O114" s="35">
         <v>1</v>
@@ -18147,7 +18144,7 @@
         <v>706</v>
       </c>
       <c r="N121" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O121" s="35">
         <v>1</v>
@@ -18268,10 +18265,10 @@
         <v>30</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18525,7 +18522,7 @@
         <v>726</v>
       </c>
       <c r="N124" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O124" s="35">
         <v>1</v>
@@ -18993,7 +18990,7 @@
         <v>382</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>204</v>
@@ -19475,18 +19472,18 @@
         <v>2</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E132" s="34"/>
       <c r="F132" s="34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G132" s="34"/>
       <c r="H132" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I132" s="33" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J132" s="33"/>
       <c r="K132" s="33" t="s">
@@ -19496,7 +19493,7 @@
         <v>22</v>
       </c>
       <c r="M132" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="N132" s="34" t="s">
         <v>848</v>
@@ -19755,7 +19752,7 @@
         <v>456</v>
       </c>
       <c r="N134" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O134" s="35">
         <v>1</v>
@@ -20609,13 +20606,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="34" t="s">
+        <v>871</v>
+      </c>
+      <c r="E141" s="34" t="s">
+        <v>870</v>
+      </c>
+      <c r="F141" s="34" t="s">
         <v>872</v>
-      </c>
-      <c r="E141" s="34" t="s">
-        <v>871</v>
-      </c>
-      <c r="F141" s="34" t="s">
-        <v>873</v>
       </c>
       <c r="G141" s="34" t="s">
         <v>137</v>
@@ -20739,7 +20736,7 @@
         <v>635</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G142" s="34" t="s">
         <v>83</v>
@@ -20772,7 +20769,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="34" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="R142" s="13"/>
       <c r="S142" s="2">
@@ -21227,51 +21224,53 @@
       <c r="AT145" s="13"/>
     </row>
     <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="36">
-        <v>0</v>
-      </c>
-      <c r="B146" s="36">
+      <c r="A146" s="33">
+        <v>0</v>
+      </c>
+      <c r="B146" s="33">
         <v>2</v>
       </c>
-      <c r="C146" s="36">
+      <c r="C146" s="33">
         <v>4</v>
       </c>
-      <c r="D146" s="37" t="s">
+      <c r="D146" s="34" t="s">
         <v>530</v>
       </c>
-      <c r="E146" s="37" t="s">
+      <c r="E146" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F146" s="37" t="s">
+      <c r="F146" s="34" t="s">
         <v>649</v>
       </c>
-      <c r="G146" s="37" t="s">
+      <c r="G146" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H146" s="37" t="s">
+      <c r="H146" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I146" s="36" t="s">
+      <c r="I146" s="33" t="s">
         <v>531</v>
       </c>
-      <c r="J146" s="36">
+      <c r="J146" s="33">
         <v>3</v>
       </c>
-      <c r="K146" s="36" t="s">
+      <c r="K146" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="L146" s="36" t="s">
+      <c r="L146" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M146" s="37" t="s">
+      <c r="M146" s="34" t="s">
         <v>668</v>
       </c>
-      <c r="N146" s="37" t="s">
-        <v>851</v>
-      </c>
-      <c r="O146" s="38"/>
-      <c r="P146" s="36"/>
-      <c r="Q146" s="37"/>
+      <c r="N146" s="34" t="s">
+        <v>883</v>
+      </c>
+      <c r="O146" s="35">
+        <v>1</v>
+      </c>
+      <c r="P146" s="33"/>
+      <c r="Q146" s="34"/>
       <c r="R146" s="13"/>
       <c r="S146" s="2">
         <f t="shared" si="55"/>
@@ -21320,7 +21319,7 @@
       </c>
       <c r="AE146" s="2">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF146" s="2">
         <f t="shared" si="51"/>
@@ -21328,7 +21327,7 @@
       </c>
       <c r="AG146" s="2">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH146" s="2">
         <f t="shared" si="53"/>
@@ -21513,7 +21512,7 @@
         <v>622</v>
       </c>
       <c r="N148" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O148" s="35">
         <v>1</v>
@@ -21639,7 +21638,7 @@
         <v>514</v>
       </c>
       <c r="N149" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O149" s="35">
         <v>1</v>
@@ -22140,7 +22139,7 @@
         <v>669</v>
       </c>
       <c r="N153" s="40" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O153" s="41"/>
       <c r="P153" s="39"/>
@@ -22502,7 +22501,7 @@
         <v>817</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22628,7 +22627,7 @@
         <v>729</v>
       </c>
       <c r="N157" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O157" s="35">
         <v>1</v>
@@ -22876,7 +22875,7 @@
         <v>843</v>
       </c>
       <c r="N159" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="O159" s="35">
         <v>1</v>
@@ -22998,7 +22997,7 @@
         <v>828</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -23124,7 +23123,7 @@
         <v>461</v>
       </c>
       <c r="N161" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O161" s="35">
         <v>1</v>
@@ -23613,7 +23612,7 @@
         <v>744</v>
       </c>
       <c r="N165" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O165" s="35">
         <v>1</v>
@@ -23965,7 +23964,7 @@
         <v>87</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>100</v>
@@ -24215,7 +24214,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G170" s="34" t="s">
         <v>82</v>
@@ -24471,7 +24470,7 @@
         <v>38</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G172" s="34" t="s">
         <v>758</v>
@@ -24751,7 +24750,7 @@
         <v>196</v>
       </c>
       <c r="N174" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O174" s="35">
         <v>1</v>
@@ -24877,7 +24876,7 @@
         <v>196</v>
       </c>
       <c r="N175" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O175" s="35">
         <v>1</v>
@@ -25872,7 +25871,7 @@
         <v>196</v>
       </c>
       <c r="N183" s="37" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O183" s="38"/>
       <c r="P183" s="36"/>
@@ -27472,7 +27471,7 @@
         <v>55</v>
       </c>
       <c r="F196" s="34" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G196" s="34" t="s">
         <v>72</v>
@@ -27481,7 +27480,7 @@
         <v>190</v>
       </c>
       <c r="I196" s="33" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J196" s="33">
         <v>4</v>
@@ -28246,7 +28245,7 @@
         <v>196</v>
       </c>
       <c r="N202" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O202" s="35">
         <v>1</v>
@@ -28372,7 +28371,7 @@
         <v>196</v>
       </c>
       <c r="N203" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O203" s="35">
         <v>1</v>
@@ -28754,7 +28753,7 @@
         <v>196</v>
       </c>
       <c r="N206" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O206" s="35">
         <v>1</v>
@@ -28880,7 +28879,7 @@
         <v>196</v>
       </c>
       <c r="N207" s="34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O207" s="35">
         <v>1</v>
@@ -29863,7 +29862,7 @@
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G215" s="34" t="s">
         <v>145</v>
@@ -30012,7 +30011,7 @@
         <v>312</v>
       </c>
       <c r="N216" s="37" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O216" s="38"/>
       <c r="P216" s="36"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A7CEA2-7177-4AAF-B659-FB453A8108AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD98D74F-3C41-45AE-B2F4-F84914019394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3323,7 +3323,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3342,8 +3342,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="Collegamento ipertestuale 2" xfId="1" xr:uid="{5B803421-0FBC-41BF-B163-75D6EF5EE395}"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232F0267-79C4-4685-890A-337DD0656400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4301650-A126-4A48-821B-74A5DA1077DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3800,15 +3800,15 @@
       </c>
       <c r="F4" s="4">
         <f>+AE6</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="4">
         <f>+AG6</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" s="3">
         <f>+E4-G4</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>16</v>
@@ -3830,15 +3830,15 @@
       </c>
       <c r="F5" s="42">
         <f>+F3+F4</f>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G5" s="42">
         <f>+G3+G4</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H5" s="42">
         <f>+H3+H4</f>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="43" t="s">
         <v>613</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="1"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="1"/>
@@ -4829,51 +4829,53 @@
       <c r="AT13" s="5"/>
     </row>
     <row r="14" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25">
-        <v>0</v>
-      </c>
-      <c r="B14" s="25">
-        <v>1</v>
-      </c>
-      <c r="C14" s="25">
-        <v>1</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="A14" s="21">
+        <v>0</v>
+      </c>
+      <c r="B14" s="21">
+        <v>1</v>
+      </c>
+      <c r="C14" s="21">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="22" t="s">
         <v>579</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="21" t="s">
         <v>578</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="21">
         <v>2</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="21">
         <v>75</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="N14" s="51" t="s">
-        <v>847</v>
-      </c>
-      <c r="O14" s="19"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="26"/>
+      <c r="N14" s="49" t="s">
+        <v>851</v>
+      </c>
+      <c r="O14" s="18">
+        <v>1</v>
+      </c>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
       <c r="R14" s="5"/>
       <c r="S14" s="1">
         <f t="shared" si="7"/>
@@ -4922,7 +4924,7 @@
       </c>
       <c r="AE14" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" s="1">
         <f t="shared" si="19"/>
@@ -4930,7 +4932,7 @@
       </c>
       <c r="AG14" s="1">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="1">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4301650-A126-4A48-821B-74A5DA1077DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F6DF98-634D-4955-A897-B9BD13D72BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3800,15 +3800,15 @@
       </c>
       <c r="F4" s="4">
         <f>+AE6</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4">
         <f>+AG6</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="3">
         <f>+E4-G4</f>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>16</v>
@@ -3830,15 +3830,15 @@
       </c>
       <c r="F5" s="42">
         <f>+F3+F4</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" s="42">
         <f>+G3+G4</f>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H5" s="42">
         <f>+H3+H4</f>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I5" s="43" t="s">
         <v>613</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="1"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="1"/>
@@ -20045,51 +20045,53 @@
       <c r="AT135" s="5"/>
     </row>
     <row r="136" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="25">
-        <v>0</v>
-      </c>
-      <c r="B136" s="25">
+      <c r="A136" s="21">
+        <v>0</v>
+      </c>
+      <c r="B136" s="21">
         <v>2</v>
       </c>
-      <c r="C136" s="25">
+      <c r="C136" s="21">
         <v>2</v>
       </c>
-      <c r="D136" s="26" t="s">
+      <c r="D136" s="22" t="s">
         <v>634</v>
       </c>
-      <c r="E136" s="26" t="s">
+      <c r="E136" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="F136" s="26" t="s">
+      <c r="F136" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="G136" s="26" t="s">
+      <c r="G136" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="H136" s="26" t="s">
+      <c r="H136" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="I136" s="25" t="s">
+      <c r="I136" s="21" t="s">
         <v>779</v>
       </c>
-      <c r="J136" s="25">
+      <c r="J136" s="21">
         <v>99</v>
       </c>
-      <c r="K136" s="25" t="s">
+      <c r="K136" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="L136" s="25" t="s">
+      <c r="L136" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="M136" s="59" t="s">
+      <c r="M136" s="57" t="s">
         <v>665</v>
       </c>
-      <c r="N136" s="51" t="s">
-        <v>846</v>
-      </c>
-      <c r="O136" s="19"/>
-      <c r="P136" s="25"/>
-      <c r="Q136" s="26"/>
+      <c r="N136" s="49" t="s">
+        <v>853</v>
+      </c>
+      <c r="O136" s="18">
+        <v>1</v>
+      </c>
+      <c r="P136" s="21"/>
+      <c r="Q136" s="22"/>
       <c r="R136" s="5"/>
       <c r="S136" s="1">
         <f t="shared" si="39"/>
@@ -20138,7 +20140,7 @@
       </c>
       <c r="AE136" s="1">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF136" s="1">
         <f t="shared" si="35"/>
@@ -20146,7 +20148,7 @@
       </c>
       <c r="AG136" s="1">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH136" s="1">
         <f t="shared" si="37"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F6DF98-634D-4955-A897-B9BD13D72BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9C4280-F075-4E68-B64A-8E152071FA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="916">
   <si>
     <t>Recensore</t>
   </si>
@@ -2657,9 +2657,6 @@
   </si>
   <si>
     <t>Fernanda D'Arienzo</t>
-  </si>
-  <si>
-    <t>bloccato per Francesca Vasciaveo</t>
   </si>
   <si>
     <t>bloccato per Catia Gribaudo</t>
@@ -3800,15 +3797,15 @@
       </c>
       <c r="F4" s="4">
         <f>+AE6</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="4">
         <f>+AG6</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3">
         <f>+E4-G4</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>16</v>
@@ -3830,15 +3827,15 @@
       </c>
       <c r="F5" s="42">
         <f>+F3+F4</f>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G5" s="42">
         <f>+G3+G4</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H5" s="42">
         <f>+H3+H4</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I5" s="43" t="s">
         <v>613</v>
@@ -3930,7 +3927,7 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="1"/>
@@ -3938,7 +3935,7 @@
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="1"/>
@@ -3999,7 +3996,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="45" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="13">
@@ -4113,7 +4110,7 @@
         <v>716</v>
       </c>
       <c r="N8" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O8" s="18">
         <v>1</v>
@@ -4367,7 +4364,7 @@
         <v>698</v>
       </c>
       <c r="N10" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O10" s="18">
         <v>1</v>
@@ -4469,7 +4466,7 @@
         <v>235</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>106</v>
@@ -4493,7 +4490,7 @@
         <v>678</v>
       </c>
       <c r="N11" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O11" s="18">
         <v>1</v>
@@ -4869,7 +4866,7 @@
         <v>194</v>
       </c>
       <c r="N14" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O14" s="18">
         <v>1</v>
@@ -4965,20 +4962,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>276</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="28" t="s">
         <v>189</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J15" s="27"/>
       <c r="K15" s="27" t="s">
@@ -5096,7 +5093,7 @@
         <v>189</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="J16" s="29">
         <v>1</v>
@@ -5233,7 +5230,7 @@
         <v>697</v>
       </c>
       <c r="N17" s="49" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O17" s="18">
         <v>1</v>
@@ -5357,7 +5354,7 @@
         <v>809</v>
       </c>
       <c r="N18" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O18" s="18">
         <v>1</v>
@@ -5983,7 +5980,7 @@
         <v>245</v>
       </c>
       <c r="N23" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O23" s="18">
         <v>1</v>
@@ -6109,7 +6106,7 @@
         <v>508</v>
       </c>
       <c r="N24" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O24" s="18">
         <v>1</v>
@@ -6235,7 +6232,7 @@
         <v>194</v>
       </c>
       <c r="N25" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O25" s="18">
         <v>1</v>
@@ -6361,7 +6358,7 @@
         <v>194</v>
       </c>
       <c r="N26" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O26" s="18">
         <v>1</v>
@@ -6737,7 +6734,7 @@
         <v>699</v>
       </c>
       <c r="N29" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O29" s="18">
         <v>1</v>
@@ -6861,7 +6858,7 @@
         <v>790</v>
       </c>
       <c r="N30" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O30" s="18">
         <v>1</v>
@@ -6987,14 +6984,14 @@
         <v>700</v>
       </c>
       <c r="N31" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O31" s="18">
         <v>1</v>
       </c>
       <c r="P31" s="21"/>
       <c r="Q31" s="22" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="1">
@@ -7115,7 +7112,7 @@
         <v>245</v>
       </c>
       <c r="N32" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O32" s="18">
         <v>1</v>
@@ -7573,22 +7570,22 @@
         <v>5</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E36" s="22" t="s">
         <v>233</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>189</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J36" s="21"/>
       <c r="K36" s="21" t="s">
@@ -7598,17 +7595,17 @@
         <v>55</v>
       </c>
       <c r="M36" s="57" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N36" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O36" s="18">
         <v>1</v>
       </c>
       <c r="P36" s="21"/>
       <c r="Q36" s="22" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="1">
@@ -7729,7 +7726,7 @@
         <v>194</v>
       </c>
       <c r="N37" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O37" s="18">
         <v>1</v>
@@ -7983,7 +7980,7 @@
         <v>791</v>
       </c>
       <c r="N39" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O39" s="18">
         <v>1</v>
@@ -8231,7 +8228,7 @@
         <v>792</v>
       </c>
       <c r="N41" s="51" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O41" s="19"/>
       <c r="P41" s="25"/>
@@ -8355,7 +8352,7 @@
         <v>692</v>
       </c>
       <c r="N42" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O42" s="18">
         <v>1</v>
@@ -9091,7 +9088,7 @@
         <v>511</v>
       </c>
       <c r="N48" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O48" s="18">
         <v>1</v>
@@ -9217,7 +9214,7 @@
         <v>676</v>
       </c>
       <c r="N49" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O49" s="18">
         <v>1</v>
@@ -9343,7 +9340,7 @@
         <v>300</v>
       </c>
       <c r="N50" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O50" s="18">
         <v>1</v>
@@ -9469,7 +9466,7 @@
         <v>194</v>
       </c>
       <c r="N51" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O51" s="18">
         <v>1</v>
@@ -9595,7 +9592,7 @@
         <v>672</v>
       </c>
       <c r="N52" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O52" s="18">
         <v>1</v>
@@ -9843,7 +9840,7 @@
         <v>300</v>
       </c>
       <c r="N54" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O54" s="18">
         <v>1</v>
@@ -9945,7 +9942,7 @@
         <v>234</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>488</v>
@@ -9969,7 +9966,7 @@
         <v>263</v>
       </c>
       <c r="N55" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O55" s="18">
         <v>1</v>
@@ -10098,7 +10095,7 @@
       <c r="O56" s="20"/>
       <c r="P56" s="23"/>
       <c r="Q56" s="24" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="1">
@@ -10189,13 +10186,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>233</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>108</v>
@@ -10204,7 +10201,7 @@
         <v>189</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J57" s="21"/>
       <c r="K57" s="21" t="s">
@@ -10679,51 +10676,53 @@
       <c r="AT60" s="5"/>
     </row>
     <row r="61" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="25">
-        <v>0</v>
-      </c>
-      <c r="B61" s="25">
-        <v>1</v>
-      </c>
-      <c r="C61" s="25">
+      <c r="A61" s="21">
+        <v>0</v>
+      </c>
+      <c r="B61" s="21">
+        <v>1</v>
+      </c>
+      <c r="C61" s="21">
         <v>5</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D61" s="22" t="s">
         <v>388</v>
       </c>
-      <c r="E61" s="26" t="s">
+      <c r="E61" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="F61" s="26" t="s">
+      <c r="F61" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="G61" s="26" t="s">
+      <c r="G61" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="H61" s="26" t="s">
+      <c r="H61" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="I61" s="25" t="s">
+      <c r="I61" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="J61" s="25">
+      <c r="J61" s="21">
         <v>5</v>
       </c>
-      <c r="K61" s="25" t="s">
+      <c r="K61" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="L61" s="25" t="s">
+      <c r="L61" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="M61" s="59" t="s">
+      <c r="M61" s="57" t="s">
         <v>673</v>
       </c>
-      <c r="N61" s="51" t="s">
-        <v>846</v>
-      </c>
-      <c r="O61" s="19"/>
-      <c r="P61" s="25"/>
-      <c r="Q61" s="26"/>
+      <c r="N61" s="49" t="s">
+        <v>852</v>
+      </c>
+      <c r="O61" s="18">
+        <v>1</v>
+      </c>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="22"/>
       <c r="R61" s="5"/>
       <c r="S61" s="1">
         <f t="shared" si="23"/>
@@ -10772,7 +10771,7 @@
       </c>
       <c r="AE61" s="1">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF61" s="1">
         <f t="shared" si="19"/>
@@ -10780,7 +10779,7 @@
       </c>
       <c r="AG61" s="1">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH61" s="1">
         <f t="shared" si="21"/>
@@ -11455,7 +11454,7 @@
         <v>675</v>
       </c>
       <c r="N67" s="49" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O67" s="18">
         <v>1</v>
@@ -11581,7 +11580,7 @@
         <v>701</v>
       </c>
       <c r="N68" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O68" s="18">
         <v>1</v>
@@ -11707,7 +11706,7 @@
         <v>194</v>
       </c>
       <c r="N69" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O69" s="18">
         <v>1</v>
@@ -11803,13 +11802,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E70" s="30" t="s">
         <v>837</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G70" s="30" t="s">
         <v>72</v>
@@ -11818,7 +11817,7 @@
         <v>189</v>
       </c>
       <c r="I70" s="29" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J70" s="29">
         <v>4</v>
@@ -11830,7 +11829,7 @@
         <v>45</v>
       </c>
       <c r="M70" s="61" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="N70" s="53"/>
       <c r="O70" s="8"/>
@@ -11953,7 +11952,7 @@
         <v>814</v>
       </c>
       <c r="N71" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O71" s="18">
         <v>1</v>
@@ -12079,7 +12078,7 @@
         <v>710</v>
       </c>
       <c r="N72" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O72" s="18">
         <v>1</v>
@@ -12205,7 +12204,7 @@
         <v>511</v>
       </c>
       <c r="N73" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O73" s="18">
         <v>1</v>
@@ -12331,7 +12330,7 @@
         <v>511</v>
       </c>
       <c r="N74" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O74" s="18">
         <v>1</v>
@@ -12698,10 +12697,10 @@
         <v>70</v>
       </c>
       <c r="M77" s="57" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="N77" s="49" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O77" s="18">
         <v>1</v>
@@ -13074,7 +13073,7 @@
       <c r="O80" s="8"/>
       <c r="P80" s="29"/>
       <c r="Q80" s="30" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="1">
@@ -13195,7 +13194,7 @@
         <v>506</v>
       </c>
       <c r="N81" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O81" s="18">
         <v>1</v>
@@ -13449,7 +13448,7 @@
         <v>247</v>
       </c>
       <c r="N83" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O83" s="18">
         <v>1</v>
@@ -13703,7 +13702,7 @@
         <v>709</v>
       </c>
       <c r="N85" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O85" s="18">
         <v>1</v>
@@ -13799,13 +13798,13 @@
         <v>6</v>
       </c>
       <c r="D86" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="E86" s="22" t="s">
         <v>875</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="F86" s="22" t="s">
         <v>876</v>
-      </c>
-      <c r="F86" s="22" t="s">
-        <v>877</v>
       </c>
       <c r="G86" s="22" t="s">
         <v>88</v>
@@ -13814,7 +13813,7 @@
         <v>189</v>
       </c>
       <c r="I86" s="21" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J86" s="21">
         <v>2</v>
@@ -13826,10 +13825,10 @@
         <v>45</v>
       </c>
       <c r="M86" s="57" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="N86" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O86" s="18">
         <v>1</v>
@@ -13952,7 +13951,7 @@
         <v>514</v>
       </c>
       <c r="N87" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O87" s="18">
         <v>1</v>
@@ -14075,7 +14074,7 @@
         <v>514</v>
       </c>
       <c r="N88" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O88" s="18">
         <v>1</v>
@@ -14201,7 +14200,7 @@
         <v>247</v>
       </c>
       <c r="N89" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O89" s="18">
         <v>1</v>
@@ -14297,20 +14296,20 @@
         <v>6</v>
       </c>
       <c r="D90" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="E90" s="22" t="s">
         <v>857</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="F90" s="22" t="s">
         <v>858</v>
-      </c>
-      <c r="F90" s="22" t="s">
-        <v>859</v>
       </c>
       <c r="G90" s="22"/>
       <c r="H90" s="22" t="s">
         <v>189</v>
       </c>
       <c r="I90" s="21" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21" t="s">
@@ -14447,7 +14446,7 @@
         <v>194</v>
       </c>
       <c r="N91" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O91" s="18">
         <v>1</v>
@@ -14573,7 +14572,7 @@
         <v>702</v>
       </c>
       <c r="N92" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O92" s="18">
         <v>1</v>
@@ -14821,7 +14820,7 @@
         <v>625</v>
       </c>
       <c r="N94" s="50" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O94" s="20">
         <v>1</v>
@@ -15212,7 +15211,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="22" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R97" s="5"/>
       <c r="S97" s="1">
@@ -15333,7 +15332,7 @@
         <v>266</v>
       </c>
       <c r="N98" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O98" s="18">
         <v>1</v>
@@ -15459,7 +15458,7 @@
         <v>266</v>
       </c>
       <c r="N99" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O99" s="18">
         <v>1</v>
@@ -15585,7 +15584,7 @@
         <v>830</v>
       </c>
       <c r="N100" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O100" s="18">
         <v>1</v>
@@ -15711,7 +15710,7 @@
         <v>194</v>
       </c>
       <c r="N101" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O101" s="18">
         <v>1</v>
@@ -15959,7 +15958,7 @@
         <v>801</v>
       </c>
       <c r="N103" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O103" s="18">
         <v>1</v>
@@ -16085,7 +16084,7 @@
         <v>561</v>
       </c>
       <c r="N104" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O104" s="18">
         <v>1</v>
@@ -16211,7 +16210,7 @@
         <v>248</v>
       </c>
       <c r="N105" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O105" s="18">
         <v>1</v>
@@ -16435,13 +16434,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E107" s="22" t="s">
         <v>69</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G107" s="22" t="s">
         <v>88</v>
@@ -16450,7 +16449,7 @@
         <v>189</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J107" s="21">
         <v>2</v>
@@ -16462,7 +16461,7 @@
         <v>5</v>
       </c>
       <c r="M107" s="57" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N107" s="49" t="s">
         <v>845</v>
@@ -16474,7 +16473,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="22" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R107" s="5"/>
       <c r="S107" s="1">
@@ -16604,7 +16603,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="22" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="R108" s="5"/>
       <c r="S108" s="1">
@@ -16695,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E109" s="22" t="s">
         <v>754</v>
@@ -17347,7 +17346,7 @@
         <v>192</v>
       </c>
       <c r="N114" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O114" s="18">
         <v>1</v>
@@ -18229,7 +18228,7 @@
         <v>704</v>
       </c>
       <c r="N121" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O121" s="18">
         <v>1</v>
@@ -18350,10 +18349,10 @@
         <v>30</v>
       </c>
       <c r="M122" s="57" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="N122" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O122" s="18">
         <v>1</v>
@@ -18607,7 +18606,7 @@
         <v>724</v>
       </c>
       <c r="N124" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O124" s="18">
         <v>1</v>
@@ -19075,7 +19074,7 @@
         <v>380</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G128" s="30" t="s">
         <v>203</v>
@@ -19557,18 +19556,18 @@
         <v>2</v>
       </c>
       <c r="D132" s="22" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="22" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G132" s="22"/>
       <c r="H132" s="22" t="s">
         <v>189</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J132" s="21"/>
       <c r="K132" s="21" t="s">
@@ -19578,7 +19577,7 @@
         <v>22</v>
       </c>
       <c r="M132" s="57" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N132" s="49" t="s">
         <v>845</v>
@@ -19837,7 +19836,7 @@
         <v>454</v>
       </c>
       <c r="N134" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O134" s="18">
         <v>1</v>
@@ -20085,7 +20084,7 @@
         <v>665</v>
       </c>
       <c r="N136" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O136" s="18">
         <v>1</v>
@@ -20693,13 +20692,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>866</v>
+      </c>
+      <c r="F141" s="22" t="s">
         <v>868</v>
-      </c>
-      <c r="E141" s="22" t="s">
-        <v>867</v>
-      </c>
-      <c r="F141" s="22" t="s">
-        <v>869</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>136</v>
@@ -20823,7 +20822,7 @@
         <v>633</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G142" s="22" t="s">
         <v>83</v>
@@ -20856,7 +20855,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="22" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="R142" s="5"/>
       <c r="S142" s="1">
@@ -21351,7 +21350,7 @@
         <v>666</v>
       </c>
       <c r="N146" s="49" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O146" s="18">
         <v>1</v>
@@ -21599,7 +21598,7 @@
         <v>620</v>
       </c>
       <c r="N148" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O148" s="18">
         <v>1</v>
@@ -21725,7 +21724,7 @@
         <v>512</v>
       </c>
       <c r="N149" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O149" s="18">
         <v>1</v>
@@ -22226,7 +22225,7 @@
         <v>667</v>
       </c>
       <c r="N153" s="50" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="O153" s="20"/>
       <c r="P153" s="23"/>
@@ -22588,7 +22587,7 @@
         <v>814</v>
       </c>
       <c r="N156" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O156" s="18">
         <v>1</v>
@@ -22714,7 +22713,7 @@
         <v>727</v>
       </c>
       <c r="N157" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O157" s="18">
         <v>1</v>
@@ -22962,7 +22961,7 @@
         <v>840</v>
       </c>
       <c r="N159" s="49" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O159" s="18">
         <v>1</v>
@@ -23084,7 +23083,7 @@
         <v>825</v>
       </c>
       <c r="N160" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O160" s="18">
         <v>1</v>
@@ -23210,7 +23209,7 @@
         <v>459</v>
       </c>
       <c r="N161" s="49" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O161" s="18">
         <v>1</v>
@@ -23330,10 +23329,10 @@
         <v>45</v>
       </c>
       <c r="M162" s="59" t="s">
+        <v>914</v>
+      </c>
+      <c r="N162" s="51" t="s">
         <v>915</v>
-      </c>
-      <c r="N162" s="51" t="s">
-        <v>916</v>
       </c>
       <c r="O162" s="19"/>
       <c r="P162" s="25"/>
@@ -23701,7 +23700,7 @@
         <v>742</v>
       </c>
       <c r="N165" s="49" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O165" s="18">
         <v>1</v>
@@ -24053,7 +24052,7 @@
         <v>87</v>
       </c>
       <c r="F168" s="30" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G168" s="30" t="s">
         <v>99</v>
@@ -24303,7 +24302,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G170" s="22" t="s">
         <v>82</v>
@@ -24559,7 +24558,7 @@
         <v>38</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G172" s="22" t="s">
         <v>756</v>
@@ -24839,7 +24838,7 @@
         <v>195</v>
       </c>
       <c r="N174" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O174" s="18">
         <v>1</v>
@@ -24950,7 +24949,7 @@
         <v>189</v>
       </c>
       <c r="I175" s="21" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="J175" s="21">
         <v>99</v>
@@ -24965,7 +24964,7 @@
         <v>195</v>
       </c>
       <c r="N175" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O175" s="18">
         <v>1</v>
@@ -25076,7 +25075,7 @@
         <v>189</v>
       </c>
       <c r="I176" s="21" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="J176" s="21"/>
       <c r="K176" s="21" t="s">
@@ -25089,7 +25088,7 @@
         <v>195</v>
       </c>
       <c r="N176" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O176" s="18">
         <v>1</v>
@@ -26084,7 +26083,7 @@
         <v>195</v>
       </c>
       <c r="N184" s="51" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="O184" s="19"/>
       <c r="P184" s="25"/>
@@ -27684,7 +27683,7 @@
         <v>55</v>
       </c>
       <c r="F197" s="22" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G197" s="22" t="s">
         <v>72</v>
@@ -27693,7 +27692,7 @@
         <v>189</v>
       </c>
       <c r="I197" s="21" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J197" s="21">
         <v>4</v>
@@ -28458,7 +28457,7 @@
         <v>195</v>
       </c>
       <c r="N203" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O203" s="18">
         <v>1</v>
@@ -28584,7 +28583,7 @@
         <v>195</v>
       </c>
       <c r="N204" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O204" s="18">
         <v>1</v>
@@ -28680,7 +28679,7 @@
         <v>7</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E205" s="22" t="s">
         <v>38</v>
@@ -28808,7 +28807,7 @@
         <v>7</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E206" s="22" t="s">
         <v>38</v>
@@ -28966,7 +28965,7 @@
         <v>195</v>
       </c>
       <c r="N207" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O207" s="18">
         <v>1</v>
@@ -29092,7 +29091,7 @@
         <v>195</v>
       </c>
       <c r="N208" s="49" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O208" s="18">
         <v>1</v>
@@ -30075,7 +30074,7 @@
         <v>55</v>
       </c>
       <c r="F216" s="22" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G216" s="22" t="s">
         <v>144</v>
@@ -30224,7 +30223,7 @@
         <v>310</v>
       </c>
       <c r="N217" s="51" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="O217" s="19"/>
       <c r="P217" s="25"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9C4280-F075-4E68-B64A-8E152071FA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C8488F-7BA6-4195-A7C8-18E98D813D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FF1390-E0B2-4305-9068-55933D53D1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E59C4C-490B-4264-A652-515C38E9910A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="916">
   <si>
     <t>Recensore</t>
   </si>
@@ -2648,9 +2648,6 @@
   </si>
   <si>
     <t>Fernanda D'Arienzo</t>
-  </si>
-  <si>
-    <t>bloccato per Catia Gribaudo</t>
   </si>
   <si>
     <t>Trattoria Tarassaco</t>
@@ -3800,15 +3797,15 @@
       </c>
       <c r="F4" s="4">
         <f>+AE6</f>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G4" s="4">
         <f>+AG6</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H4" s="3">
         <f>+E4-G4</f>
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>16</v>
@@ -3830,15 +3827,15 @@
       </c>
       <c r="F5" s="42">
         <f>+F3+F4</f>
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G5" s="42">
         <f>+G3+G4</f>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H5" s="42">
         <f>+H3+H4</f>
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I5" s="43" t="s">
         <v>612</v>
@@ -3930,7 +3927,7 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="1"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="1"/>
@@ -3938,7 +3935,7 @@
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="1"/>
@@ -3999,7 +3996,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="45" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="13">
@@ -4113,7 +4110,7 @@
         <v>715</v>
       </c>
       <c r="N8" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O8" s="18">
         <v>1</v>
@@ -4367,7 +4364,7 @@
         <v>697</v>
       </c>
       <c r="N10" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O10" s="18">
         <v>1</v>
@@ -4469,7 +4466,7 @@
         <v>234</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>105</v>
@@ -4493,7 +4490,7 @@
         <v>677</v>
       </c>
       <c r="N11" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O11" s="18">
         <v>1</v>
@@ -4619,7 +4616,7 @@
         <v>193</v>
       </c>
       <c r="N12" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O12" s="18">
         <v>1</v>
@@ -4995,7 +4992,7 @@
         <v>193</v>
       </c>
       <c r="N15" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O15" s="18">
         <v>1</v>
@@ -5091,20 +5088,20 @@
         <v>2</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>275</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
         <v>188</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="J16" s="27"/>
       <c r="K16" s="27" t="s">
@@ -5222,7 +5219,7 @@
         <v>188</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="J17" s="29">
         <v>1</v>
@@ -5359,7 +5356,7 @@
         <v>696</v>
       </c>
       <c r="N18" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O18" s="18">
         <v>1</v>
@@ -5483,7 +5480,7 @@
         <v>806</v>
       </c>
       <c r="N19" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O19" s="18">
         <v>1</v>
@@ -5951,18 +5948,18 @@
         <v>2</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="22" t="s">
         <v>188</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
@@ -5972,10 +5969,10 @@
         <v>50</v>
       </c>
       <c r="M23" s="57" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N23" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O23" s="18">
         <v>1</v>
@@ -6229,7 +6226,7 @@
         <v>244</v>
       </c>
       <c r="N25" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O25" s="18">
         <v>1</v>
@@ -6355,7 +6352,7 @@
         <v>507</v>
       </c>
       <c r="N26" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O26" s="18">
         <v>1</v>
@@ -6481,7 +6478,7 @@
         <v>193</v>
       </c>
       <c r="N27" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O27" s="18">
         <v>1</v>
@@ -6857,7 +6854,7 @@
         <v>698</v>
       </c>
       <c r="N30" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O30" s="18">
         <v>1</v>
@@ -6981,7 +6978,7 @@
         <v>787</v>
       </c>
       <c r="N31" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O31" s="18">
         <v>1</v>
@@ -7107,14 +7104,14 @@
         <v>699</v>
       </c>
       <c r="N32" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O32" s="18">
         <v>1</v>
       </c>
       <c r="P32" s="21"/>
       <c r="Q32" s="22" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="1">
@@ -7235,7 +7232,7 @@
         <v>244</v>
       </c>
       <c r="N33" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O33" s="18">
         <v>1</v>
@@ -7723,7 +7720,7 @@
         <v>193</v>
       </c>
       <c r="N37" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O37" s="18">
         <v>1</v>
@@ -7977,7 +7974,7 @@
         <v>788</v>
       </c>
       <c r="N39" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O39" s="18">
         <v>1</v>
@@ -8185,51 +8182,53 @@
       <c r="AT40" s="5"/>
     </row>
     <row r="41" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="25">
-        <v>0</v>
-      </c>
-      <c r="B41" s="25">
-        <v>1</v>
-      </c>
-      <c r="C41" s="25">
+      <c r="A41" s="21">
+        <v>0</v>
+      </c>
+      <c r="B41" s="21">
+        <v>1</v>
+      </c>
+      <c r="C41" s="21">
         <v>3</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="22" t="s">
         <v>748</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="22" t="s">
         <v>753</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="22" t="s">
         <v>742</v>
       </c>
-      <c r="G41" s="26" t="s">
+      <c r="G41" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="H41" s="26" t="s">
+      <c r="H41" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="I41" s="25" t="s">
+      <c r="I41" s="21" t="s">
         <v>743</v>
       </c>
-      <c r="J41" s="25">
-        <v>1</v>
-      </c>
-      <c r="K41" s="25" t="s">
+      <c r="J41" s="21">
+        <v>1</v>
+      </c>
+      <c r="K41" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="L41" s="25">
+      <c r="L41" s="21">
         <v>50</v>
       </c>
-      <c r="M41" s="59" t="s">
+      <c r="M41" s="57" t="s">
         <v>789</v>
       </c>
-      <c r="N41" s="51" t="s">
-        <v>843</v>
-      </c>
-      <c r="O41" s="19"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="26"/>
+      <c r="N41" s="49" t="s">
+        <v>846</v>
+      </c>
+      <c r="O41" s="18">
+        <v>1</v>
+      </c>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="22"/>
       <c r="R41" s="5"/>
       <c r="S41" s="1">
         <f t="shared" si="23"/>
@@ -8278,7 +8277,7 @@
       </c>
       <c r="AE41" s="1">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" s="1">
         <f t="shared" si="19"/>
@@ -8286,7 +8285,7 @@
       </c>
       <c r="AG41" s="1">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH41" s="1">
         <f t="shared" si="21"/>
@@ -8349,7 +8348,7 @@
         <v>691</v>
       </c>
       <c r="N42" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O42" s="18">
         <v>1</v>
@@ -9085,7 +9084,7 @@
         <v>510</v>
       </c>
       <c r="N48" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O48" s="18">
         <v>1</v>
@@ -9211,7 +9210,7 @@
         <v>675</v>
       </c>
       <c r="N49" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O49" s="18">
         <v>1</v>
@@ -9337,7 +9336,7 @@
         <v>299</v>
       </c>
       <c r="N50" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O50" s="18">
         <v>1</v>
@@ -9463,7 +9462,7 @@
         <v>193</v>
       </c>
       <c r="N51" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O51" s="18">
         <v>1</v>
@@ -9589,7 +9588,7 @@
         <v>671</v>
       </c>
       <c r="N52" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O52" s="18">
         <v>1</v>
@@ -9837,7 +9836,7 @@
         <v>299</v>
       </c>
       <c r="N54" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O54" s="18">
         <v>1</v>
@@ -9939,7 +9938,7 @@
         <v>233</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>487</v>
@@ -9963,7 +9962,7 @@
         <v>262</v>
       </c>
       <c r="N55" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O55" s="18">
         <v>1</v>
@@ -10092,7 +10091,7 @@
       <c r="O56" s="20"/>
       <c r="P56" s="23"/>
       <c r="Q56" s="24" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="1">
@@ -10183,13 +10182,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>232</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>107</v>
@@ -10198,7 +10197,7 @@
         <v>188</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J57" s="21"/>
       <c r="K57" s="21" t="s">
@@ -10683,22 +10682,22 @@
         <v>5</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E61" s="22" t="s">
         <v>232</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>188</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J61" s="21"/>
       <c r="K61" s="21" t="s">
@@ -10708,17 +10707,17 @@
         <v>55</v>
       </c>
       <c r="M61" s="57" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="N61" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O61" s="18">
         <v>1</v>
       </c>
       <c r="P61" s="21"/>
       <c r="Q61" s="22" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="R61" s="5"/>
       <c r="S61" s="1">
@@ -10839,7 +10838,7 @@
         <v>672</v>
       </c>
       <c r="N62" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O62" s="18">
         <v>1</v>
@@ -11577,7 +11576,7 @@
         <v>674</v>
       </c>
       <c r="N68" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O68" s="18">
         <v>1</v>
@@ -11703,7 +11702,7 @@
         <v>700</v>
       </c>
       <c r="N69" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O69" s="18">
         <v>1</v>
@@ -11829,7 +11828,7 @@
         <v>193</v>
       </c>
       <c r="N70" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O70" s="18">
         <v>1</v>
@@ -11925,13 +11924,13 @@
         <v>5</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E71" s="30" t="s">
         <v>834</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G71" s="30" t="s">
         <v>71</v>
@@ -11940,7 +11939,7 @@
         <v>188</v>
       </c>
       <c r="I71" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J71" s="29">
         <v>4</v>
@@ -11952,7 +11951,7 @@
         <v>45</v>
       </c>
       <c r="M71" s="61" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N71" s="53"/>
       <c r="O71" s="8"/>
@@ -12075,7 +12074,7 @@
         <v>811</v>
       </c>
       <c r="N72" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O72" s="18">
         <v>1</v>
@@ -12201,7 +12200,7 @@
         <v>709</v>
       </c>
       <c r="N73" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O73" s="18">
         <v>1</v>
@@ -12327,7 +12326,7 @@
         <v>510</v>
       </c>
       <c r="N74" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O74" s="18">
         <v>1</v>
@@ -12694,10 +12693,10 @@
         <v>70</v>
       </c>
       <c r="M77" s="57" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N77" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O77" s="18">
         <v>1</v>
@@ -13070,7 +13069,7 @@
       <c r="O80" s="8"/>
       <c r="P80" s="29"/>
       <c r="Q80" s="30" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="1">
@@ -13191,7 +13190,7 @@
         <v>505</v>
       </c>
       <c r="N81" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O81" s="18">
         <v>1</v>
@@ -13445,7 +13444,7 @@
         <v>246</v>
       </c>
       <c r="N83" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O83" s="18">
         <v>1</v>
@@ -13571,7 +13570,7 @@
         <v>723</v>
       </c>
       <c r="N84" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O84" s="18">
         <v>1</v>
@@ -13825,7 +13824,7 @@
         <v>708</v>
       </c>
       <c r="N86" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O86" s="18">
         <v>1</v>
@@ -13918,13 +13917,13 @@
         <v>6</v>
       </c>
       <c r="D87" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="E87" s="22" t="s">
         <v>871</v>
       </c>
-      <c r="E87" s="22" t="s">
+      <c r="F87" s="22" t="s">
         <v>872</v>
-      </c>
-      <c r="F87" s="22" t="s">
-        <v>873</v>
       </c>
       <c r="G87" s="22" t="s">
         <v>87</v>
@@ -13933,7 +13932,7 @@
         <v>188</v>
       </c>
       <c r="I87" s="21" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J87" s="21">
         <v>2</v>
@@ -13945,10 +13944,10 @@
         <v>45</v>
       </c>
       <c r="M87" s="57" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="N87" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O87" s="18">
         <v>1</v>
@@ -14071,7 +14070,7 @@
         <v>513</v>
       </c>
       <c r="N88" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O88" s="18">
         <v>1</v>
@@ -14197,7 +14196,7 @@
         <v>513</v>
       </c>
       <c r="N89" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O89" s="18">
         <v>1</v>
@@ -14323,7 +14322,7 @@
         <v>246</v>
       </c>
       <c r="N90" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O90" s="18">
         <v>1</v>
@@ -14419,20 +14418,20 @@
         <v>6</v>
       </c>
       <c r="D91" s="22" t="s">
+        <v>852</v>
+      </c>
+      <c r="E91" s="22" t="s">
         <v>853</v>
       </c>
-      <c r="E91" s="22" t="s">
+      <c r="F91" s="22" t="s">
         <v>854</v>
-      </c>
-      <c r="F91" s="22" t="s">
-        <v>855</v>
       </c>
       <c r="G91" s="22"/>
       <c r="H91" s="22" t="s">
         <v>188</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21" t="s">
@@ -14569,7 +14568,7 @@
         <v>193</v>
       </c>
       <c r="N92" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O92" s="18">
         <v>1</v>
@@ -14695,7 +14694,7 @@
         <v>701</v>
       </c>
       <c r="N93" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O93" s="18">
         <v>1</v>
@@ -14943,7 +14942,7 @@
         <v>624</v>
       </c>
       <c r="N95" s="50" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O95" s="20">
         <v>1</v>
@@ -15334,7 +15333,7 @@
         <v>1</v>
       </c>
       <c r="Q98" s="22" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="R98" s="5"/>
       <c r="S98" s="1">
@@ -15455,7 +15454,7 @@
         <v>265</v>
       </c>
       <c r="N99" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O99" s="18">
         <v>1</v>
@@ -15581,7 +15580,7 @@
         <v>265</v>
       </c>
       <c r="N100" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O100" s="18">
         <v>1</v>
@@ -15707,7 +15706,7 @@
         <v>827</v>
       </c>
       <c r="N101" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O101" s="18">
         <v>1</v>
@@ -15833,7 +15832,7 @@
         <v>193</v>
       </c>
       <c r="N102" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O102" s="18">
         <v>1</v>
@@ -16081,7 +16080,7 @@
         <v>798</v>
       </c>
       <c r="N104" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O104" s="18">
         <v>1</v>
@@ -16207,7 +16206,7 @@
         <v>560</v>
       </c>
       <c r="N105" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O105" s="18">
         <v>1</v>
@@ -16333,7 +16332,7 @@
         <v>247</v>
       </c>
       <c r="N106" s="49" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O106" s="18">
         <v>1</v>
@@ -16557,13 +16556,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E108" s="22" t="s">
         <v>68</v>
       </c>
       <c r="F108" s="22" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G108" s="22" t="s">
         <v>87</v>
@@ -16572,7 +16571,7 @@
         <v>188</v>
       </c>
       <c r="I108" s="21" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J108" s="21">
         <v>2</v>
@@ -16584,7 +16583,7 @@
         <v>5</v>
       </c>
       <c r="M108" s="57" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="N108" s="49" t="s">
         <v>842</v>
@@ -16596,7 +16595,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="22" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="R108" s="5"/>
       <c r="S108" s="1">
@@ -16726,7 +16725,7 @@
         <v>1</v>
       </c>
       <c r="Q109" s="22" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="R109" s="5"/>
       <c r="S109" s="1">
@@ -16817,7 +16816,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E110" s="22" t="s">
         <v>752</v>
@@ -17469,7 +17468,7 @@
         <v>191</v>
       </c>
       <c r="N115" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O115" s="18">
         <v>1</v>
@@ -18351,7 +18350,7 @@
         <v>703</v>
       </c>
       <c r="N122" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O122" s="18">
         <v>1</v>
@@ -18472,10 +18471,10 @@
         <v>30</v>
       </c>
       <c r="M123" s="57" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N123" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O123" s="18">
         <v>1</v>
@@ -19071,7 +19070,7 @@
         <v>379</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G128" s="30" t="s">
         <v>202</v>
@@ -19553,18 +19552,18 @@
         <v>2</v>
       </c>
       <c r="D132" s="22" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="22" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G132" s="22"/>
       <c r="H132" s="22" t="s">
         <v>188</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J132" s="21"/>
       <c r="K132" s="21" t="s">
@@ -19574,7 +19573,7 @@
         <v>22</v>
       </c>
       <c r="M132" s="57" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N132" s="49" t="s">
         <v>842</v>
@@ -19833,7 +19832,7 @@
         <v>453</v>
       </c>
       <c r="N134" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O134" s="18">
         <v>1</v>
@@ -20081,7 +20080,7 @@
         <v>664</v>
       </c>
       <c r="N136" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O136" s="18">
         <v>1</v>
@@ -20689,13 +20688,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="22" t="s">
+        <v>863</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>862</v>
+      </c>
+      <c r="F141" s="22" t="s">
         <v>864</v>
-      </c>
-      <c r="E141" s="22" t="s">
-        <v>863</v>
-      </c>
-      <c r="F141" s="22" t="s">
-        <v>865</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>135</v>
@@ -20819,7 +20818,7 @@
         <v>632</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G142" s="22" t="s">
         <v>82</v>
@@ -20852,7 +20851,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="22" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R142" s="5"/>
       <c r="S142" s="1">
@@ -21061,51 +21060,53 @@
       <c r="AT143" s="5"/>
     </row>
     <row r="144" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="25">
-        <v>0</v>
-      </c>
-      <c r="B144" s="25">
+      <c r="A144" s="21">
+        <v>0</v>
+      </c>
+      <c r="B144" s="21">
         <v>2</v>
       </c>
-      <c r="C144" s="25">
+      <c r="C144" s="21">
         <v>3</v>
       </c>
-      <c r="D144" s="26" t="s">
+      <c r="D144" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="E144" s="26" t="s">
+      <c r="E144" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F144" s="26" t="s">
+      <c r="F144" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="G144" s="26" t="s">
+      <c r="G144" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="H144" s="26" t="s">
+      <c r="H144" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="I144" s="25" t="s">
+      <c r="I144" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="25">
+      <c r="J144" s="21">
         <v>2</v>
       </c>
-      <c r="K144" s="25" t="s">
+      <c r="K144" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="L144" s="25" t="s">
+      <c r="L144" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="M144" s="59" t="s">
+      <c r="M144" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="N144" s="51" t="s">
+      <c r="N144" s="49" t="s">
         <v>869</v>
       </c>
-      <c r="O144" s="19"/>
-      <c r="P144" s="25"/>
-      <c r="Q144" s="26"/>
+      <c r="O144" s="18">
+        <v>1</v>
+      </c>
+      <c r="P144" s="21"/>
+      <c r="Q144" s="22"/>
       <c r="R144" s="5"/>
       <c r="S144" s="1">
         <f t="shared" ref="S144:S208" si="71">IF(J144=$S$7,1,0)</f>
@@ -21154,7 +21155,7 @@
       </c>
       <c r="AE144" s="1">
         <f t="shared" ref="AE144:AE208" si="82">O144*(1-P144)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF144" s="1">
         <f t="shared" si="67"/>
@@ -21162,7 +21163,7 @@
       </c>
       <c r="AG144" s="1">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH144" s="1">
         <f t="shared" si="69"/>
@@ -21347,7 +21348,7 @@
         <v>665</v>
       </c>
       <c r="N146" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O146" s="18">
         <v>1</v>
@@ -21595,7 +21596,7 @@
         <v>619</v>
       </c>
       <c r="N148" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O148" s="18">
         <v>1</v>
@@ -21721,7 +21722,7 @@
         <v>511</v>
       </c>
       <c r="N149" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O149" s="18">
         <v>1</v>
@@ -22222,7 +22223,7 @@
         <v>666</v>
       </c>
       <c r="N153" s="50" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O153" s="20"/>
       <c r="P153" s="23"/>
@@ -22584,7 +22585,7 @@
         <v>811</v>
       </c>
       <c r="N156" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O156" s="18">
         <v>1</v>
@@ -22710,7 +22711,7 @@
         <v>726</v>
       </c>
       <c r="N157" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O157" s="18">
         <v>1</v>
@@ -22958,7 +22959,7 @@
         <v>837</v>
       </c>
       <c r="N159" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="O159" s="18">
         <v>1</v>
@@ -23080,7 +23081,7 @@
         <v>822</v>
       </c>
       <c r="N160" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O160" s="18">
         <v>1</v>
@@ -23206,7 +23207,7 @@
         <v>458</v>
       </c>
       <c r="N161" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O161" s="18">
         <v>1</v>
@@ -23326,10 +23327,10 @@
         <v>45</v>
       </c>
       <c r="M162" s="59" t="s">
+        <v>910</v>
+      </c>
+      <c r="N162" s="51" t="s">
         <v>911</v>
-      </c>
-      <c r="N162" s="51" t="s">
-        <v>912</v>
       </c>
       <c r="O162" s="19"/>
       <c r="P162" s="25"/>
@@ -23697,7 +23698,7 @@
         <v>741</v>
       </c>
       <c r="N165" s="49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="O165" s="18">
         <v>1</v>
@@ -24049,7 +24050,7 @@
         <v>86</v>
       </c>
       <c r="F168" s="30" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G168" s="30" t="s">
         <v>98</v>
@@ -24299,7 +24300,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G170" s="22" t="s">
         <v>81</v>
@@ -24555,7 +24556,7 @@
         <v>38</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G172" s="22" t="s">
         <v>754</v>
@@ -24835,7 +24836,7 @@
         <v>194</v>
       </c>
       <c r="N174" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O174" s="18">
         <v>1</v>
@@ -24946,7 +24947,7 @@
         <v>188</v>
       </c>
       <c r="I175" s="21" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J175" s="21">
         <v>99</v>
@@ -24961,7 +24962,7 @@
         <v>194</v>
       </c>
       <c r="N175" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O175" s="18">
         <v>1</v>
@@ -25072,7 +25073,7 @@
         <v>188</v>
       </c>
       <c r="I176" s="21" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J176" s="21"/>
       <c r="K176" s="21" t="s">
@@ -25085,7 +25086,7 @@
         <v>194</v>
       </c>
       <c r="N176" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O176" s="18">
         <v>1</v>
@@ -26039,53 +26040,54 @@
       <c r="AS183" s="2"/>
       <c r="AT183" s="2"/>
     </row>
-    <row r="184" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="25">
-        <v>0</v>
-      </c>
-      <c r="B184" s="25">
+    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="21">
+        <v>0</v>
+      </c>
+      <c r="B184" s="21">
         <v>2</v>
       </c>
-      <c r="C184" s="25">
+      <c r="C184" s="21">
         <v>7</v>
       </c>
-      <c r="D184" s="26" t="s">
+      <c r="D184" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="E184" s="26" t="s">
+      <c r="E184" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F184" s="26" t="s">
+      <c r="F184" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="G184" s="26" t="s">
+      <c r="G184" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="H184" s="26" t="s">
+      <c r="H184" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="I184" s="25" t="s">
+      <c r="I184" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="J184" s="25">
+      <c r="J184" s="21">
         <v>99</v>
       </c>
-      <c r="K184" s="25" t="s">
+      <c r="K184" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="L184" s="25">
+      <c r="L184" s="21">
         <v>4</v>
       </c>
-      <c r="M184" s="59" t="s">
+      <c r="M184" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="N184" s="51" t="s">
+      <c r="N184" s="49" t="s">
         <v>869</v>
       </c>
-      <c r="O184" s="19"/>
-      <c r="P184" s="25"/>
-      <c r="Q184" s="26"/>
-      <c r="R184" s="5"/>
+      <c r="O184" s="18">
+        <v>1</v>
+      </c>
+      <c r="P184" s="21"/>
+      <c r="Q184" s="22"/>
       <c r="S184" s="1">
         <f t="shared" si="71"/>
         <v>0</v>
@@ -26126,14 +26128,13 @@
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="AC184" s="1"/>
       <c r="AD184" s="1">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AE184" s="1">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF184" s="1">
         <f t="shared" si="67"/>
@@ -26141,7 +26142,7 @@
       </c>
       <c r="AG184" s="1">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH184" s="1">
         <f t="shared" si="69"/>
@@ -26151,17 +26152,16 @@
         <f t="shared" si="70"/>
         <v>1</v>
       </c>
-      <c r="AJ184" s="5"/>
-      <c r="AK184" s="5"/>
-      <c r="AL184" s="5"/>
-      <c r="AM184" s="5"/>
-      <c r="AN184" s="5"/>
-      <c r="AO184" s="5"/>
-      <c r="AP184" s="5"/>
-      <c r="AQ184" s="5"/>
-      <c r="AR184" s="5"/>
-      <c r="AS184" s="5"/>
-      <c r="AT184" s="5"/>
+      <c r="AK184" s="2"/>
+      <c r="AL184" s="2"/>
+      <c r="AM184" s="2"/>
+      <c r="AN184" s="2"/>
+      <c r="AO184" s="2"/>
+      <c r="AP184" s="2"/>
+      <c r="AQ184" s="2"/>
+      <c r="AR184" s="2"/>
+      <c r="AS184" s="2"/>
+      <c r="AT184" s="2"/>
     </row>
     <row r="185" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="29">
@@ -27680,7 +27680,7 @@
         <v>55</v>
       </c>
       <c r="F197" s="22" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G197" s="22" t="s">
         <v>71</v>
@@ -27689,7 +27689,7 @@
         <v>188</v>
       </c>
       <c r="I197" s="21" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J197" s="21">
         <v>4</v>
@@ -28454,7 +28454,7 @@
         <v>194</v>
       </c>
       <c r="N203" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O203" s="18">
         <v>1</v>
@@ -28580,7 +28580,7 @@
         <v>194</v>
       </c>
       <c r="N204" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O204" s="18">
         <v>1</v>
@@ -28676,7 +28676,7 @@
         <v>7</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E205" s="22" t="s">
         <v>38</v>
@@ -28804,7 +28804,7 @@
         <v>7</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E206" s="22" t="s">
         <v>38</v>
@@ -28962,7 +28962,7 @@
         <v>194</v>
       </c>
       <c r="N207" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O207" s="18">
         <v>1</v>
@@ -29088,7 +29088,7 @@
         <v>194</v>
       </c>
       <c r="N208" s="49" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O208" s="18">
         <v>1</v>
@@ -30071,7 +30071,7 @@
         <v>55</v>
       </c>
       <c r="F216" s="22" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G216" s="22" t="s">
         <v>143</v>
@@ -30179,53 +30179,54 @@
       <c r="AS216" s="2"/>
       <c r="AT216" s="2"/>
     </row>
-    <row r="217" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="25">
-        <v>0</v>
-      </c>
-      <c r="B217" s="25">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="21">
+        <v>0</v>
+      </c>
+      <c r="B217" s="21">
         <v>2</v>
       </c>
-      <c r="C217" s="25">
+      <c r="C217" s="21">
         <v>7</v>
       </c>
-      <c r="D217" s="26" t="s">
+      <c r="D217" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="E217" s="26" t="s">
+      <c r="E217" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="F217" s="26" t="s">
+      <c r="F217" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="G217" s="26" t="s">
+      <c r="G217" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="H217" s="26" t="s">
+      <c r="H217" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="I217" s="25" t="s">
+      <c r="I217" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="J217" s="25">
-        <v>1</v>
-      </c>
-      <c r="K217" s="25" t="s">
+      <c r="J217" s="21">
+        <v>1</v>
+      </c>
+      <c r="K217" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="L217" s="25" t="s">
+      <c r="L217" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="M217" s="59" t="s">
+      <c r="M217" s="57" t="s">
         <v>309</v>
       </c>
-      <c r="N217" s="51" t="s">
+      <c r="N217" s="49" t="s">
         <v>869</v>
       </c>
-      <c r="O217" s="19"/>
-      <c r="P217" s="25"/>
-      <c r="Q217" s="26"/>
-      <c r="R217" s="5"/>
+      <c r="O217" s="18">
+        <v>1</v>
+      </c>
+      <c r="P217" s="21"/>
+      <c r="Q217" s="22"/>
       <c r="S217" s="1">
         <f t="shared" si="103"/>
         <v>1</v>
@@ -30266,14 +30267,13 @@
         <f t="shared" si="112"/>
         <v>0</v>
       </c>
-      <c r="AC217" s="1"/>
       <c r="AD217" s="1">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="AE217" s="1">
         <f t="shared" si="114"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF217" s="1">
         <f t="shared" si="99"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="AG217" s="1">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH217" s="1">
         <f t="shared" si="101"/>
@@ -30291,17 +30291,16 @@
         <f t="shared" si="102"/>
         <v>1</v>
       </c>
-      <c r="AJ217" s="5"/>
-      <c r="AK217" s="5"/>
-      <c r="AL217" s="5"/>
-      <c r="AM217" s="5"/>
-      <c r="AN217" s="5"/>
-      <c r="AO217" s="5"/>
-      <c r="AP217" s="5"/>
-      <c r="AQ217" s="5"/>
-      <c r="AR217" s="5"/>
-      <c r="AS217" s="5"/>
-      <c r="AT217" s="5"/>
+      <c r="AK217" s="2"/>
+      <c r="AL217" s="2"/>
+      <c r="AM217" s="2"/>
+      <c r="AN217" s="2"/>
+      <c r="AO217" s="2"/>
+      <c r="AP217" s="2"/>
+      <c r="AQ217" s="2"/>
+      <c r="AR217" s="2"/>
+      <c r="AS217" s="2"/>
+      <c r="AT217" s="2"/>
     </row>
     <row r="218" spans="1:46" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="21">
